--- a/dpr_output.xlsx
+++ b/dpr_output.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\Client\C$\Games\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{CD2D324F-6DA2-4D50-8DB6-606D947B43F9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{108AA5B4-D484-4C52-B53B-FFF03B471B24}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11620" xr2:uid="{4BB7744D-70ED-4F43-96F3-771A2176E148}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11620" xr2:uid="{E8AA4F23-053D-4C4C-950B-10DF39FF97F5}"/>
   </bookViews>
   <sheets>
     <sheet name="DPR ( 26-APR-2025 )" sheetId="3" r:id="rId1"/>
@@ -241,7 +241,7 @@
     <t>The respective asset has been relinquished on 31.AUG.2019</t>
   </si>
   <si>
-    <t>Report Generated On: 05.MAY.2026 At 13:48:01</t>
+    <t>Report Generated On: 05.MAY.2026 At 14:07:54</t>
   </si>
   <si>
     <t>Production Date</t>
@@ -1043,7 +1043,7 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-9381-42B2-BCD7-609A8016B6D0}"/>
+              <c16:uniqueId val="{00000000-5BA0-4F93-BC3A-68CC9A5F9B11}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -1156,7 +1156,7 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000001-9381-42B2-BCD7-609A8016B6D0}"/>
+              <c16:uniqueId val="{00000001-5BA0-4F93-BC3A-68CC9A5F9B11}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -1170,11 +1170,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="1680560447"/>
-        <c:axId val="1680542207"/>
+        <c:axId val="1432058767"/>
+        <c:axId val="1432077007"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="1680560447"/>
+        <c:axId val="1432058767"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1184,7 +1184,7 @@
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="1680542207"/>
+        <c:crossAx val="1432077007"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -1192,7 +1192,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="1680542207"/>
+        <c:axId val="1432077007"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1221,7 +1221,7 @@
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="1680560447"/>
+        <c:crossAx val="1432058767"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -1269,7 +1269,7 @@
         <xdr:cNvPr id="3" name="Picture 2">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{210E8B9C-0BDE-FF3F-76BF-91DDF2B63F5B}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0A4157D9-6D4E-2072-AC5D-DE4A5DA4B792}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1324,7 +1324,7 @@
         <xdr:cNvPr id="2" name="Chart 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{94C0717E-DBBF-4DAE-EE5F-05D44324F4FA}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B7F40165-3EBC-4696-D946-C5F75D02523A}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1661,7 +1661,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5FFB2BDF-B7BA-4815-9FE4-512CDB5EBB02}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5FCDC798-C853-4030-BE19-2A004144EF4A}">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
@@ -6957,7 +6957,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8670DC70-01BF-4EE7-9342-72CCA21D8FFE}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BE113E13-10F2-4C18-BC5A-30C8A7FA6C78}">
   <dimension ref="B2:AA4"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
@@ -7135,7 +7135,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{76B4198C-4C9E-4431-B392-E9A6E1537D80}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{13DC2D66-F967-48B1-B173-20C25F3F7E08}">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>

--- a/dpr_output.xlsx
+++ b/dpr_output.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\Client\C$\Games\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{108AA5B4-D484-4C52-B53B-FFF03B471B24}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{525F3DC5-5A31-4DAA-A9B9-2D191EDFC43C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11620" xr2:uid="{E8AA4F23-053D-4C4C-950B-10DF39FF97F5}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11620" xr2:uid="{B0BFE8DA-5C9E-47CE-8388-EBF88F311DF5}"/>
   </bookViews>
   <sheets>
     <sheet name="DPR ( 26-APR-2025 )" sheetId="3" r:id="rId1"/>
@@ -241,7 +241,7 @@
     <t>The respective asset has been relinquished on 31.AUG.2019</t>
   </si>
   <si>
-    <t>Report Generated On: 05.MAY.2026 At 14:07:54</t>
+    <t>Report Generated On: 05.MAY.2026 At 14:19:03</t>
   </si>
   <si>
     <t>Production Date</t>
@@ -1043,7 +1043,7 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-5BA0-4F93-BC3A-68CC9A5F9B11}"/>
+              <c16:uniqueId val="{00000000-FC04-434C-ABC5-074B59AAFE53}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -1156,7 +1156,7 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000001-5BA0-4F93-BC3A-68CC9A5F9B11}"/>
+              <c16:uniqueId val="{00000001-FC04-434C-ABC5-074B59AAFE53}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -1170,11 +1170,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="1432058767"/>
-        <c:axId val="1432077007"/>
+        <c:axId val="91258623"/>
+        <c:axId val="91253823"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="1432058767"/>
+        <c:axId val="91258623"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1184,7 +1184,7 @@
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="1432077007"/>
+        <c:crossAx val="91253823"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -1192,7 +1192,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="1432077007"/>
+        <c:axId val="91253823"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1221,7 +1221,7 @@
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="1432058767"/>
+        <c:crossAx val="91258623"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -1269,7 +1269,7 @@
         <xdr:cNvPr id="3" name="Picture 2">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0A4157D9-6D4E-2072-AC5D-DE4A5DA4B792}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A5866758-2AA4-868F-E4A8-C489194978E7}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1324,7 +1324,7 @@
         <xdr:cNvPr id="2" name="Chart 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B7F40165-3EBC-4696-D946-C5F75D02523A}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{ADE19527-2D02-7CC4-F370-12D6F75A9BF7}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1661,7 +1661,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5FCDC798-C853-4030-BE19-2A004144EF4A}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{03173059-0721-4908-AB4C-E425567242F7}">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
@@ -6957,7 +6957,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BE113E13-10F2-4C18-BC5A-30C8A7FA6C78}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{17D7BA4D-5193-45BB-9213-5260DEED91FD}">
   <dimension ref="B2:AA4"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
@@ -7135,7 +7135,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{13DC2D66-F967-48B1-B173-20C25F3F7E08}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{48A853F1-BBDC-4F1A-934F-F018FA5A486C}">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>

--- a/dpr_output.xlsx
+++ b/dpr_output.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\Client\C$\Games\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{525F3DC5-5A31-4DAA-A9B9-2D191EDFC43C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{8171FAEB-2636-4F1C-B8CA-F326B2D98916}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11620" xr2:uid="{B0BFE8DA-5C9E-47CE-8388-EBF88F311DF5}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11620" xr2:uid="{BFFD3A74-B3C5-4E8B-A846-F9A9019E218F}"/>
   </bookViews>
   <sheets>
     <sheet name="DPR ( 26-APR-2025 )" sheetId="3" r:id="rId1"/>
@@ -241,7 +241,7 @@
     <t>The respective asset has been relinquished on 31.AUG.2019</t>
   </si>
   <si>
-    <t>Report Generated On: 05.MAY.2026 At 14:19:03</t>
+    <t>Report Generated On: 05.MAY.2026 At 15:16:50</t>
   </si>
   <si>
     <t>Production Date</t>
@@ -1043,7 +1043,7 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-FC04-434C-ABC5-074B59AAFE53}"/>
+              <c16:uniqueId val="{00000000-FFBD-44AA-89B9-6815EA3C0887}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -1156,7 +1156,7 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000001-FC04-434C-ABC5-074B59AAFE53}"/>
+              <c16:uniqueId val="{00000001-FFBD-44AA-89B9-6815EA3C0887}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -1170,11 +1170,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="91258623"/>
-        <c:axId val="91253823"/>
+        <c:axId val="1615774063"/>
+        <c:axId val="1615779343"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="91258623"/>
+        <c:axId val="1615774063"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1184,7 +1184,7 @@
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="91253823"/>
+        <c:crossAx val="1615779343"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -1192,7 +1192,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="91253823"/>
+        <c:axId val="1615779343"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1221,7 +1221,7 @@
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="91258623"/>
+        <c:crossAx val="1615774063"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -1269,7 +1269,7 @@
         <xdr:cNvPr id="3" name="Picture 2">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A5866758-2AA4-868F-E4A8-C489194978E7}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{DE13ADA2-4AB4-EF05-FD10-4D991B90D0B5}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1324,7 +1324,7 @@
         <xdr:cNvPr id="2" name="Chart 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{ADE19527-2D02-7CC4-F370-12D6F75A9BF7}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{EBFD640B-58B0-DCF1-7ED9-2BDF2A738A46}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1661,7 +1661,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{03173059-0721-4908-AB4C-E425567242F7}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{15FDBAA6-E2E8-45B6-A56E-D15775C35872}">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
@@ -6957,7 +6957,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{17D7BA4D-5193-45BB-9213-5260DEED91FD}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DEC218CB-7293-4D96-BC8C-20BF3868E7A1}">
   <dimension ref="B2:AA4"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
@@ -7135,7 +7135,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{48A853F1-BBDC-4F1A-934F-F018FA5A486C}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8EBB207C-48A1-4065-BEC8-41F213DAA7F9}">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>

--- a/dpr_output.xlsx
+++ b/dpr_output.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\Client\C$\Games\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{8171FAEB-2636-4F1C-B8CA-F326B2D98916}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{62D4A19F-1320-4311-BBFE-367CC8AD03AB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11620" xr2:uid="{BFFD3A74-B3C5-4E8B-A846-F9A9019E218F}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11620" xr2:uid="{F7A3C6ED-11B7-4FDC-BAF5-3444D96B2ABD}"/>
   </bookViews>
   <sheets>
     <sheet name="DPR ( 26-APR-2025 )" sheetId="3" r:id="rId1"/>
@@ -241,7 +241,7 @@
     <t>The respective asset has been relinquished on 31.AUG.2019</t>
   </si>
   <si>
-    <t>Report Generated On: 05.MAY.2026 At 15:16:50</t>
+    <t>Report Generated On: 05.MAY.2026 At 17:29:53</t>
   </si>
   <si>
     <t>Production Date</t>
@@ -1043,7 +1043,7 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-FFBD-44AA-89B9-6815EA3C0887}"/>
+              <c16:uniqueId val="{00000000-CDC4-4B63-9F7F-ACB1412B9D9B}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -1156,7 +1156,7 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000001-FFBD-44AA-89B9-6815EA3C0887}"/>
+              <c16:uniqueId val="{00000001-CDC4-4B63-9F7F-ACB1412B9D9B}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -1170,11 +1170,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="1615774063"/>
-        <c:axId val="1615779343"/>
+        <c:axId val="102866064"/>
+        <c:axId val="102876624"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="1615774063"/>
+        <c:axId val="102866064"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1184,7 +1184,7 @@
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="1615779343"/>
+        <c:crossAx val="102876624"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -1192,7 +1192,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="1615779343"/>
+        <c:axId val="102876624"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1221,7 +1221,7 @@
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="1615774063"/>
+        <c:crossAx val="102866064"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -1269,7 +1269,7 @@
         <xdr:cNvPr id="3" name="Picture 2">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{DE13ADA2-4AB4-EF05-FD10-4D991B90D0B5}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{56760B52-63D0-E1B2-59FF-14BCA992D23D}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1324,7 +1324,7 @@
         <xdr:cNvPr id="2" name="Chart 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{EBFD640B-58B0-DCF1-7ED9-2BDF2A738A46}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7AD744F0-EBBA-A743-C351-882846243642}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1661,7 +1661,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{15FDBAA6-E2E8-45B6-A56E-D15775C35872}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3579DC19-43A9-41C4-AA60-4F6510C66799}">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
@@ -6271,7 +6271,7 @@
         <v>0</v>
       </c>
       <c r="F58" s="73">
-        <v>0.31992392040200002</v>
+        <v>0.319923941002</v>
       </c>
       <c r="G58" s="73">
         <v>0.34495581952339999</v>
@@ -6286,7 +6286,7 @@
         <v>2.8107466400002998</v>
       </c>
       <c r="K58" s="73">
-        <v>1.6813375202506</v>
+        <v>1.6813375540005999</v>
       </c>
       <c r="L58" s="73">
         <v>0</v>
@@ -6301,7 +6301,7 @@
         <v>4.3063639999699997E-2</v>
       </c>
       <c r="P58" s="73">
-        <v>25.114539301098802</v>
+        <v>25.114539355448802</v>
       </c>
       <c r="Q58" s="73">
         <v>8.863335E-3</v>
@@ -6319,22 +6319,22 @@
         <v>0</v>
       </c>
       <c r="V58" s="73">
-        <v>6.7149959999999998E-4</v>
+        <v>6.7150979999999999E-4</v>
       </c>
       <c r="W58" s="73">
         <v>1.1346769200000001E-2</v>
       </c>
       <c r="X58" s="73">
-        <v>0.63879086491000003</v>
+        <v>0.63879087099999998</v>
       </c>
       <c r="Y58" s="73">
-        <v>0.33091316883999999</v>
+        <v>0.33091316500000001</v>
       </c>
       <c r="Z58" s="73">
         <v>3.8841001600000001E-2</v>
       </c>
       <c r="AA58" s="73">
-        <v>0.71459088299999995</v>
+        <v>0.71459090199999997</v>
       </c>
       <c r="AB58" s="73">
         <v>1.3850370022</v>
@@ -6349,10 +6349,10 @@
         <v>1.1461828504</v>
       </c>
       <c r="AF58" s="73">
-        <v>4.4145742186500003</v>
+        <v>4.4145742501000003</v>
       </c>
       <c r="AG58" s="73">
-        <v>29.537976854748798</v>
+        <v>29.537976940548798</v>
       </c>
     </row>
     <row r="59" spans="1:33" x14ac:dyDescent="0.35">
@@ -6424,16 +6424,16 @@
         <v>6.9766825999999999E-3</v>
       </c>
       <c r="X59" s="73">
-        <v>0.61933886718999998</v>
+        <v>0.61933886699999996</v>
       </c>
       <c r="Y59" s="73">
-        <v>0.27731972279</v>
+        <v>0.27731972399999999</v>
       </c>
       <c r="Z59" s="73">
         <v>0.1002750027</v>
       </c>
       <c r="AA59" s="73">
-        <v>0.70981551440000001</v>
+        <v>0.70981551099999995</v>
       </c>
       <c r="AB59" s="73">
         <v>1.4684396805</v>
@@ -6448,10 +6448,10 @@
         <v>0.53936415029999996</v>
       </c>
       <c r="AF59" s="73">
-        <v>3.86664032348</v>
+        <v>3.8666403211000002</v>
       </c>
       <c r="AG59" s="73">
-        <v>25.652194247174901</v>
+        <v>25.652194244794899</v>
       </c>
     </row>
     <row r="60" spans="1:33" x14ac:dyDescent="0.35">
@@ -6957,7 +6957,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DEC218CB-7293-4D96-BC8C-20BF3868E7A1}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C7B3D473-F0B0-4669-8DBB-C0C495BDB026}">
   <dimension ref="B2:AA4"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
@@ -7135,7 +7135,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8EBB207C-48A1-4065-BEC8-41F213DAA7F9}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EB66D978-51BC-42B5-883D-E3CDB73E3685}">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>

--- a/dpr_output.xlsx
+++ b/dpr_output.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\Client\C$\Games\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{62D4A19F-1320-4311-BBFE-367CC8AD03AB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{56CE8D4D-448F-429F-BEBC-1C39C5C68EDF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11620" xr2:uid="{F7A3C6ED-11B7-4FDC-BAF5-3444D96B2ABD}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11620" xr2:uid="{D3239D66-DB38-4E11-9BDB-C855921B397C}"/>
   </bookViews>
   <sheets>
     <sheet name="DPR ( 26-APR-2025 )" sheetId="3" r:id="rId1"/>
@@ -241,7 +241,7 @@
     <t>The respective asset has been relinquished on 31.AUG.2019</t>
   </si>
   <si>
-    <t>Report Generated On: 05.MAY.2026 At 17:29:53</t>
+    <t>Report Generated On: 05.MAY.2026 At 17:47:11</t>
   </si>
   <si>
     <t>Production Date</t>
@@ -1043,7 +1043,7 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-CDC4-4B63-9F7F-ACB1412B9D9B}"/>
+              <c16:uniqueId val="{00000000-B3DD-46DB-9054-2116542E4B56}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -1156,7 +1156,7 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000001-CDC4-4B63-9F7F-ACB1412B9D9B}"/>
+              <c16:uniqueId val="{00000001-B3DD-46DB-9054-2116542E4B56}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -1170,11 +1170,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="102866064"/>
-        <c:axId val="102876624"/>
+        <c:axId val="1398245824"/>
+        <c:axId val="1398247264"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="102866064"/>
+        <c:axId val="1398245824"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1184,7 +1184,7 @@
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="102876624"/>
+        <c:crossAx val="1398247264"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -1192,7 +1192,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="102876624"/>
+        <c:axId val="1398247264"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1221,7 +1221,7 @@
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="102866064"/>
+        <c:crossAx val="1398245824"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -1269,7 +1269,7 @@
         <xdr:cNvPr id="3" name="Picture 2">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{56760B52-63D0-E1B2-59FF-14BCA992D23D}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B5244630-5CB7-16D7-1F3B-DF5B56FDC4D4}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1324,7 +1324,7 @@
         <xdr:cNvPr id="2" name="Chart 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7AD744F0-EBBA-A743-C351-882846243642}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{FE2169EE-8B88-EDC0-B415-0278FEBC9D41}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1661,7 +1661,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3579DC19-43A9-41C4-AA60-4F6510C66799}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{835FD688-C3B5-4C02-89C1-38165EEB6E89}">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
@@ -6957,7 +6957,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C7B3D473-F0B0-4669-8DBB-C0C495BDB026}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9C173845-B738-44DB-89B4-8676D5D3D42D}">
   <dimension ref="B2:AA4"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
@@ -7135,7 +7135,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EB66D978-51BC-42B5-883D-E3CDB73E3685}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{577B0C2F-D881-4519-B2A7-067378C1DCB2}">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>

--- a/dpr_output.xlsx
+++ b/dpr_output.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\Client\C$\Games\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{56CE8D4D-448F-429F-BEBC-1C39C5C68EDF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{8B53F7CA-F024-4615-818A-153C481ABAF3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11620" xr2:uid="{D3239D66-DB38-4E11-9BDB-C855921B397C}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11620" xr2:uid="{FB0B9A19-FA51-4275-8EBC-CE9B47799BC2}"/>
   </bookViews>
   <sheets>
     <sheet name="DPR ( 26-APR-2025 )" sheetId="3" r:id="rId1"/>
@@ -241,7 +241,7 @@
     <t>The respective asset has been relinquished on 31.AUG.2019</t>
   </si>
   <si>
-    <t>Report Generated On: 05.MAY.2026 At 17:47:11</t>
+    <t>Report Generated On: 05.MAY.2026 At 18:18:08</t>
   </si>
   <si>
     <t>Production Date</t>
@@ -1043,7 +1043,7 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-B3DD-46DB-9054-2116542E4B56}"/>
+              <c16:uniqueId val="{00000000-42E6-4D8F-923B-7657998DACB1}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -1156,7 +1156,7 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000001-B3DD-46DB-9054-2116542E4B56}"/>
+              <c16:uniqueId val="{00000001-42E6-4D8F-923B-7657998DACB1}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -1170,11 +1170,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="1398245824"/>
-        <c:axId val="1398247264"/>
+        <c:axId val="340158767"/>
+        <c:axId val="340159727"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="1398245824"/>
+        <c:axId val="340158767"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1184,7 +1184,7 @@
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="1398247264"/>
+        <c:crossAx val="340159727"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -1192,7 +1192,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="1398247264"/>
+        <c:axId val="340159727"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1221,7 +1221,7 @@
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="1398245824"/>
+        <c:crossAx val="340158767"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -1269,7 +1269,7 @@
         <xdr:cNvPr id="3" name="Picture 2">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B5244630-5CB7-16D7-1F3B-DF5B56FDC4D4}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{78E2582E-4407-9BB1-CB44-ACABBB5839E5}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1324,7 +1324,7 @@
         <xdr:cNvPr id="2" name="Chart 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{FE2169EE-8B88-EDC0-B415-0278FEBC9D41}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2476D1B9-5D34-38B7-F447-ED87E478063B}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1661,7 +1661,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{835FD688-C3B5-4C02-89C1-38165EEB6E89}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{74344C26-B4A6-4006-9DD9-7F24917F7B8E}">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
@@ -6271,7 +6271,7 @@
         <v>0</v>
       </c>
       <c r="F58" s="73">
-        <v>0.319923941002</v>
+        <v>0.37930772700199999</v>
       </c>
       <c r="G58" s="73">
         <v>0.34495581952339999</v>
@@ -6280,13 +6280,13 @@
         <v>0.1635629999988</v>
       </c>
       <c r="I58" s="73">
-        <v>18.088745599999999</v>
+        <v>12.111018709</v>
       </c>
       <c r="J58" s="73">
         <v>2.8107466400002998</v>
       </c>
       <c r="K58" s="73">
-        <v>1.6813375540005999</v>
+        <v>6.4717870810006</v>
       </c>
       <c r="L58" s="73">
         <v>0</v>
@@ -6301,7 +6301,7 @@
         <v>4.3063639999699997E-2</v>
       </c>
       <c r="P58" s="73">
-        <v>25.114539355448802</v>
+        <v>23.9866457774488</v>
       </c>
       <c r="Q58" s="73">
         <v>8.863335E-3</v>
@@ -6319,22 +6319,22 @@
         <v>0</v>
       </c>
       <c r="V58" s="73">
-        <v>6.7150979999999999E-4</v>
+        <v>7.8348480000000004E-4</v>
       </c>
       <c r="W58" s="73">
         <v>1.1346769200000001E-2</v>
       </c>
       <c r="X58" s="73">
-        <v>0.63879087099999998</v>
+        <v>3.757593323</v>
       </c>
       <c r="Y58" s="73">
-        <v>0.33091316500000001</v>
+        <v>1.946548052</v>
       </c>
       <c r="Z58" s="73">
         <v>3.8841001600000001E-2</v>
       </c>
       <c r="AA58" s="73">
-        <v>0.71459090199999997</v>
+        <v>3.5729544149999999</v>
       </c>
       <c r="AB58" s="73">
         <v>1.3850370022</v>
@@ -6349,10 +6349,10 @@
         <v>1.1461828504</v>
       </c>
       <c r="AF58" s="73">
-        <v>4.4145742501000003</v>
+        <v>12.0074870771</v>
       </c>
       <c r="AG58" s="73">
-        <v>29.537976940548798</v>
+        <v>36.002996189548803</v>
       </c>
     </row>
     <row r="59" spans="1:33" x14ac:dyDescent="0.35">
@@ -6379,7 +6379,7 @@
         <v>0.18657599999819999</v>
       </c>
       <c r="I59" s="73">
-        <v>16.1513144</v>
+        <v>10.812312607000001</v>
       </c>
       <c r="J59" s="73">
         <v>2.6806080600006998</v>
@@ -6400,7 +6400,7 @@
         <v>5.25066799998E-2</v>
       </c>
       <c r="P59" s="73">
-        <v>21.7782985736943</v>
+        <v>16.439296780694299</v>
       </c>
       <c r="Q59" s="73">
         <v>7.2553500005999999E-3</v>
@@ -6424,16 +6424,16 @@
         <v>6.9766825999999999E-3</v>
       </c>
       <c r="X59" s="73">
-        <v>0.61933886699999996</v>
+        <v>3.643169807</v>
       </c>
       <c r="Y59" s="73">
-        <v>0.27731972399999999</v>
+        <v>1.6312924870000001</v>
       </c>
       <c r="Z59" s="73">
         <v>0.1002750027</v>
       </c>
       <c r="AA59" s="73">
-        <v>0.70981551099999995</v>
+        <v>3.5490775719999998</v>
       </c>
       <c r="AB59" s="73">
         <v>1.4684396805</v>
@@ -6448,10 +6448,10 @@
         <v>0.53936415029999996</v>
       </c>
       <c r="AF59" s="73">
-        <v>3.8666403211000002</v>
+        <v>11.083706085099999</v>
       </c>
       <c r="AG59" s="73">
-        <v>25.652194244794899</v>
+        <v>27.530258215794898</v>
       </c>
     </row>
     <row r="60" spans="1:33" x14ac:dyDescent="0.35">
@@ -6568,7 +6568,7 @@
         <v>0</v>
       </c>
       <c r="F61" s="73">
-        <v>0.66062318900000006</v>
+        <v>0.66012030700000002</v>
       </c>
       <c r="G61" s="73">
         <v>8.5999999999999993E-2</v>
@@ -6598,7 +6598,7 @@
         <v>7.4999999999999997E-2</v>
       </c>
       <c r="P61" s="73">
-        <v>7.1756231890000004</v>
+        <v>7.1751203070000003</v>
       </c>
       <c r="Q61" s="73">
         <v>3.0000000000000001E-3</v>
@@ -6649,7 +6649,7 @@
         <v>3.34</v>
       </c>
       <c r="AG61" s="73">
-        <v>10.518623188999999</v>
+        <v>10.518120307</v>
       </c>
     </row>
     <row r="62" spans="1:33" x14ac:dyDescent="0.35">
@@ -6957,7 +6957,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9C173845-B738-44DB-89B4-8676D5D3D42D}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6C3B6FD5-124C-4854-B980-518CBDEE5B8C}">
   <dimension ref="B2:AA4"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
@@ -7135,7 +7135,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{577B0C2F-D881-4519-B2A7-067378C1DCB2}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{68F2691C-D33A-42D9-9847-5349DCF58108}">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>

--- a/dpr_output.xlsx
+++ b/dpr_output.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\Client\C$\Games\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{8B53F7CA-F024-4615-818A-153C481ABAF3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{799FCD5C-5AD0-46C0-8237-B01DC31B4E06}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11620" xr2:uid="{FB0B9A19-FA51-4275-8EBC-CE9B47799BC2}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11620" xr2:uid="{4229A121-2F16-45E8-A43A-4BC0456766AE}"/>
   </bookViews>
   <sheets>
     <sheet name="DPR ( 26-APR-2025 )" sheetId="3" r:id="rId1"/>
@@ -241,7 +241,7 @@
     <t>The respective asset has been relinquished on 31.AUG.2019</t>
   </si>
   <si>
-    <t>Report Generated On: 05.MAY.2026 At 18:18:08</t>
+    <t>Report Generated On: 05.MAY.2026 At 19:04:53</t>
   </si>
   <si>
     <t>Production Date</t>
@@ -1043,7 +1043,7 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-42E6-4D8F-923B-7657998DACB1}"/>
+              <c16:uniqueId val="{00000000-8437-4661-8CCE-58E4471A0629}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -1156,7 +1156,7 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000001-42E6-4D8F-923B-7657998DACB1}"/>
+              <c16:uniqueId val="{00000001-8437-4661-8CCE-58E4471A0629}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -1170,11 +1170,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="340158767"/>
-        <c:axId val="340159727"/>
+        <c:axId val="2076349007"/>
+        <c:axId val="2076346127"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="340158767"/>
+        <c:axId val="2076349007"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1184,7 +1184,7 @@
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="340159727"/>
+        <c:crossAx val="2076346127"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -1192,7 +1192,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="340159727"/>
+        <c:axId val="2076346127"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1221,7 +1221,7 @@
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="340158767"/>
+        <c:crossAx val="2076349007"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -1269,7 +1269,7 @@
         <xdr:cNvPr id="3" name="Picture 2">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{78E2582E-4407-9BB1-CB44-ACABBB5839E5}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0145BA94-3106-EF27-1449-09C271A4E487}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1324,7 +1324,7 @@
         <xdr:cNvPr id="2" name="Chart 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2476D1B9-5D34-38B7-F447-ED87E478063B}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3885E87C-C863-0E7F-000C-C7072078F6AF}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1661,7 +1661,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{74344C26-B4A6-4006-9DD9-7F24917F7B8E}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D95DDF4B-6A8B-4136-88D4-A15DD42345FF}">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
@@ -6280,13 +6280,13 @@
         <v>0.1635629999988</v>
       </c>
       <c r="I58" s="73">
-        <v>12.111018709</v>
+        <v>12.238664146</v>
       </c>
       <c r="J58" s="73">
         <v>2.8107466400002998</v>
       </c>
       <c r="K58" s="73">
-        <v>6.4717870810006</v>
+        <v>2.4206854510006002</v>
       </c>
       <c r="L58" s="73">
         <v>0</v>
@@ -6301,7 +6301,7 @@
         <v>4.3063639999699997E-2</v>
       </c>
       <c r="P58" s="73">
-        <v>23.9866457774488</v>
+        <v>20.0631895844488</v>
       </c>
       <c r="Q58" s="73">
         <v>8.863335E-3</v>
@@ -6352,7 +6352,7 @@
         <v>12.0074870771</v>
       </c>
       <c r="AG58" s="73">
-        <v>36.002996189548803</v>
+        <v>32.079539996548803</v>
       </c>
     </row>
     <row r="59" spans="1:33" x14ac:dyDescent="0.35">
@@ -6379,7 +6379,7 @@
         <v>0.18657599999819999</v>
       </c>
       <c r="I59" s="73">
-        <v>10.812312607000001</v>
+        <v>10.927817578000001</v>
       </c>
       <c r="J59" s="73">
         <v>2.6806080600006998</v>
@@ -6400,7 +6400,7 @@
         <v>5.25066799998E-2</v>
       </c>
       <c r="P59" s="73">
-        <v>16.439296780694299</v>
+        <v>16.554801751694299</v>
       </c>
       <c r="Q59" s="73">
         <v>7.2553500005999999E-3</v>
@@ -6451,7 +6451,7 @@
         <v>11.083706085099999</v>
       </c>
       <c r="AG59" s="73">
-        <v>27.530258215794898</v>
+        <v>27.645763186794898</v>
       </c>
     </row>
     <row r="60" spans="1:33" x14ac:dyDescent="0.35">
@@ -6957,7 +6957,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6C3B6FD5-124C-4854-B980-518CBDEE5B8C}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FCB3E974-24F5-4664-97A3-16414539BEB4}">
   <dimension ref="B2:AA4"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
@@ -7135,7 +7135,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{68F2691C-D33A-42D9-9847-5349DCF58108}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{24E1436D-BAD0-4F31-951F-D71F7844E3FB}">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>

--- a/dpr_output.xlsx
+++ b/dpr_output.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\Client\C$\Games\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{799FCD5C-5AD0-46C0-8237-B01DC31B4E06}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{08577C4E-2CFB-4366-98BE-AC842765D68C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11620" xr2:uid="{4229A121-2F16-45E8-A43A-4BC0456766AE}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11620" xr2:uid="{EEBEE938-6112-4C20-975F-47F137F04402}"/>
   </bookViews>
   <sheets>
     <sheet name="DPR ( 26-APR-2025 )" sheetId="3" r:id="rId1"/>
@@ -241,7 +241,7 @@
     <t>The respective asset has been relinquished on 31.AUG.2019</t>
   </si>
   <si>
-    <t>Report Generated On: 05.MAY.2026 At 19:04:53</t>
+    <t>Report Generated On: 05.MAY.2026 At 19:20:55</t>
   </si>
   <si>
     <t>Production Date</t>
@@ -1043,7 +1043,7 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-8437-4661-8CCE-58E4471A0629}"/>
+              <c16:uniqueId val="{00000000-3441-42E0-8D07-8855EBD01036}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -1156,7 +1156,7 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000001-8437-4661-8CCE-58E4471A0629}"/>
+              <c16:uniqueId val="{00000001-3441-42E0-8D07-8855EBD01036}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -1170,11 +1170,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="2076349007"/>
-        <c:axId val="2076346127"/>
+        <c:axId val="1417377264"/>
+        <c:axId val="1417362384"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="2076349007"/>
+        <c:axId val="1417377264"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1184,7 +1184,7 @@
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="2076346127"/>
+        <c:crossAx val="1417362384"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -1192,7 +1192,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="2076346127"/>
+        <c:axId val="1417362384"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1221,7 +1221,7 @@
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="2076349007"/>
+        <c:crossAx val="1417377264"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -1269,7 +1269,7 @@
         <xdr:cNvPr id="3" name="Picture 2">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0145BA94-3106-EF27-1449-09C271A4E487}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{85C2715E-735D-9373-9674-0C608F127C64}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1324,7 +1324,7 @@
         <xdr:cNvPr id="2" name="Chart 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3885E87C-C863-0E7F-000C-C7072078F6AF}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E0415BC3-F6DB-7CE0-E1E5-63944DF15A03}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1661,7 +1661,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D95DDF4B-6A8B-4136-88D4-A15DD42345FF}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D06779AE-22DA-4EAC-85EF-C89D5B75A0DA}">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
@@ -6319,22 +6319,22 @@
         <v>0</v>
       </c>
       <c r="V58" s="73">
-        <v>7.8348480000000004E-4</v>
+        <v>6.7150979999999999E-4</v>
       </c>
       <c r="W58" s="73">
         <v>1.1346769200000001E-2</v>
       </c>
       <c r="X58" s="73">
-        <v>3.757593323</v>
+        <v>0.63879087099999998</v>
       </c>
       <c r="Y58" s="73">
-        <v>1.946548052</v>
+        <v>0.33091316500000001</v>
       </c>
       <c r="Z58" s="73">
         <v>3.8841001600000001E-2</v>
       </c>
       <c r="AA58" s="73">
-        <v>3.5729544149999999</v>
+        <v>0.71459090199999997</v>
       </c>
       <c r="AB58" s="73">
         <v>1.3850370022</v>
@@ -6349,10 +6349,10 @@
         <v>1.1461828504</v>
       </c>
       <c r="AF58" s="73">
-        <v>12.0074870771</v>
+        <v>4.4145742501000003</v>
       </c>
       <c r="AG58" s="73">
-        <v>32.079539996548803</v>
+        <v>24.4866271695488</v>
       </c>
     </row>
     <row r="59" spans="1:33" x14ac:dyDescent="0.35">
@@ -6424,16 +6424,16 @@
         <v>6.9766825999999999E-3</v>
       </c>
       <c r="X59" s="73">
-        <v>3.643169807</v>
+        <v>0.61933886699999996</v>
       </c>
       <c r="Y59" s="73">
-        <v>1.6312924870000001</v>
+        <v>0.27731972399999999</v>
       </c>
       <c r="Z59" s="73">
         <v>0.1002750027</v>
       </c>
       <c r="AA59" s="73">
-        <v>3.5490775719999998</v>
+        <v>0.70981551099999995</v>
       </c>
       <c r="AB59" s="73">
         <v>1.4684396805</v>
@@ -6448,10 +6448,10 @@
         <v>0.53936415029999996</v>
       </c>
       <c r="AF59" s="73">
-        <v>11.083706085099999</v>
+        <v>3.8666403211000002</v>
       </c>
       <c r="AG59" s="73">
-        <v>27.645763186794898</v>
+        <v>20.428697422794901</v>
       </c>
     </row>
     <row r="60" spans="1:33" x14ac:dyDescent="0.35">
@@ -6957,7 +6957,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FCB3E974-24F5-4664-97A3-16414539BEB4}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{15365BFE-D786-4509-93EA-A235425B0495}">
   <dimension ref="B2:AA4"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
@@ -7135,7 +7135,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{24E1436D-BAD0-4F31-951F-D71F7844E3FB}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5DF238ED-D622-4120-B185-976B33CEA7D1}">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>

--- a/dpr_output.xlsx
+++ b/dpr_output.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\Client\C$\Games\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{08577C4E-2CFB-4366-98BE-AC842765D68C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{529746F2-9A1E-46EB-BEB3-11F83000BF62}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11620" xr2:uid="{EEBEE938-6112-4C20-975F-47F137F04402}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11620" xr2:uid="{A35706B0-4B6C-4BBC-8C91-736D5C0AA45B}"/>
   </bookViews>
   <sheets>
     <sheet name="DPR ( 26-APR-2025 )" sheetId="3" r:id="rId1"/>
@@ -241,7 +241,7 @@
     <t>The respective asset has been relinquished on 31.AUG.2019</t>
   </si>
   <si>
-    <t>Report Generated On: 05.MAY.2026 At 19:20:55</t>
+    <t>Report Generated On: 05.MAY.2026 At 19:56:15</t>
   </si>
   <si>
     <t>Production Date</t>
@@ -1043,7 +1043,7 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-3441-42E0-8D07-8855EBD01036}"/>
+              <c16:uniqueId val="{00000000-ED87-4518-B8CC-D72C07FC6FF3}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -1156,7 +1156,7 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000001-3441-42E0-8D07-8855EBD01036}"/>
+              <c16:uniqueId val="{00000001-ED87-4518-B8CC-D72C07FC6FF3}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -1170,11 +1170,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="1417377264"/>
-        <c:axId val="1417362384"/>
+        <c:axId val="1152591840"/>
+        <c:axId val="1152616800"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="1417377264"/>
+        <c:axId val="1152591840"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1184,7 +1184,7 @@
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="1417362384"/>
+        <c:crossAx val="1152616800"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -1192,7 +1192,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="1417362384"/>
+        <c:axId val="1152616800"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1221,7 +1221,7 @@
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="1417377264"/>
+        <c:crossAx val="1152591840"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -1269,7 +1269,7 @@
         <xdr:cNvPr id="3" name="Picture 2">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{85C2715E-735D-9373-9674-0C608F127C64}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B7D19E43-8170-DF22-09CD-BEABB0E37585}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1324,7 +1324,7 @@
         <xdr:cNvPr id="2" name="Chart 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E0415BC3-F6DB-7CE0-E1E5-63944DF15A03}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{17EC0EFC-2288-E94B-E968-BC9D0AA9E946}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1661,7 +1661,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D06779AE-22DA-4EAC-85EF-C89D5B75A0DA}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8E517340-92B0-4FE4-B87D-40DC154FB187}">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
@@ -6957,7 +6957,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{15365BFE-D786-4509-93EA-A235425B0495}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{88DC987D-72C2-4230-80A3-8E7A79A5E685}">
   <dimension ref="B2:AA4"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
@@ -7135,7 +7135,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5DF238ED-D622-4120-B185-976B33CEA7D1}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AFDEFDE5-4AE9-4A0D-AE25-689495A6F5CB}">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
@@ -7221,10 +7221,4 @@
   </customProperties>
   <drawing r:id="rId3"/>
 </worksheet>
-</file>
-
-<file path=docMetadata/LabelInfo.xml><?xml version="1.0" encoding="utf-8"?>
-<clbl:labelList xmlns:clbl="http://schemas.microsoft.com/office/2020/mipLabelMetadata">
-  <clbl:label id="{0cf7ac0a-4681-4823-ab0b-04ef02c5f873}" enabled="1" method="Standard" siteId="{42f7676c-f455-423c-82f6-dc2d99791af7}" contentBits="0" removed="0"/>
-</clbl:labelList>
 </file>
--- a/dpr_output.xlsx
+++ b/dpr_output.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\Client\C$\Games\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{529746F2-9A1E-46EB-BEB3-11F83000BF62}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{EF2B2DFB-A12E-442A-97E6-5B74B55330C8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11620" xr2:uid="{A35706B0-4B6C-4BBC-8C91-736D5C0AA45B}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11620" xr2:uid="{58A654DE-5467-484A-A500-C3B4C187D5F7}"/>
   </bookViews>
   <sheets>
     <sheet name="DPR ( 26-APR-2025 )" sheetId="3" r:id="rId1"/>
@@ -241,7 +241,7 @@
     <t>The respective asset has been relinquished on 31.AUG.2019</t>
   </si>
   <si>
-    <t>Report Generated On: 05.MAY.2026 At 19:56:15</t>
+    <t>Report Generated On: 05.MAY.2026 At 20:16:23</t>
   </si>
   <si>
     <t>Production Date</t>
@@ -1043,7 +1043,7 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-ED87-4518-B8CC-D72C07FC6FF3}"/>
+              <c16:uniqueId val="{00000000-C04C-4F16-8B1A-6A1A27A2CE8A}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -1156,7 +1156,7 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000001-ED87-4518-B8CC-D72C07FC6FF3}"/>
+              <c16:uniqueId val="{00000001-C04C-4F16-8B1A-6A1A27A2CE8A}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -1170,11 +1170,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="1152591840"/>
-        <c:axId val="1152616800"/>
+        <c:axId val="598204799"/>
+        <c:axId val="598213919"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="1152591840"/>
+        <c:axId val="598204799"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1184,7 +1184,7 @@
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="1152616800"/>
+        <c:crossAx val="598213919"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -1192,7 +1192,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="1152616800"/>
+        <c:axId val="598213919"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1221,7 +1221,7 @@
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="1152591840"/>
+        <c:crossAx val="598204799"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -1269,7 +1269,7 @@
         <xdr:cNvPr id="3" name="Picture 2">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B7D19E43-8170-DF22-09CD-BEABB0E37585}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{CA99818E-B13E-F8AD-2541-885D6E2A363B}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1324,7 +1324,7 @@
         <xdr:cNvPr id="2" name="Chart 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{17EC0EFC-2288-E94B-E968-BC9D0AA9E946}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{85C6F46E-9BE0-DD2D-92B2-E03FD3C06186}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1661,7 +1661,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8E517340-92B0-4FE4-B87D-40DC154FB187}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{183A7D64-942A-474A-988C-B4B337309CE5}">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
@@ -6957,7 +6957,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{88DC987D-72C2-4230-80A3-8E7A79A5E685}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{49D3A113-E06F-4C4E-A1ED-A2B7571C770A}">
   <dimension ref="B2:AA4"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
@@ -7135,7 +7135,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AFDEFDE5-4AE9-4A0D-AE25-689495A6F5CB}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{65EF99B4-5433-4C23-8873-268ACC398FA2}">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>

--- a/dpr_output.xlsx
+++ b/dpr_output.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\Client\C$\Games\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{EF2B2DFB-A12E-442A-97E6-5B74B55330C8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{2C6DE591-D9A5-4643-B97B-045D9770E758}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11620" xr2:uid="{58A654DE-5467-484A-A500-C3B4C187D5F7}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11620" xr2:uid="{28C784D1-3351-4F72-9E93-DC187BDEC92C}"/>
   </bookViews>
   <sheets>
     <sheet name="DPR ( 26-APR-2025 )" sheetId="3" r:id="rId1"/>
@@ -241,7 +241,7 @@
     <t>The respective asset has been relinquished on 31.AUG.2019</t>
   </si>
   <si>
-    <t>Report Generated On: 05.MAY.2026 At 20:16:23</t>
+    <t>Report Generated On: 05.MAY.2026 At 20:43:55</t>
   </si>
   <si>
     <t>Production Date</t>
@@ -1043,7 +1043,7 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-C04C-4F16-8B1A-6A1A27A2CE8A}"/>
+              <c16:uniqueId val="{00000000-238F-445A-B224-54FAF9273F8A}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -1156,7 +1156,7 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000001-C04C-4F16-8B1A-6A1A27A2CE8A}"/>
+              <c16:uniqueId val="{00000001-238F-445A-B224-54FAF9273F8A}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -1170,11 +1170,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="598204799"/>
-        <c:axId val="598213919"/>
+        <c:axId val="871583263"/>
+        <c:axId val="871597183"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="598204799"/>
+        <c:axId val="871583263"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1184,7 +1184,7 @@
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="598213919"/>
+        <c:crossAx val="871597183"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -1192,7 +1192,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="598213919"/>
+        <c:axId val="871597183"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1221,7 +1221,7 @@
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="598204799"/>
+        <c:crossAx val="871583263"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -1269,7 +1269,7 @@
         <xdr:cNvPr id="3" name="Picture 2">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{CA99818E-B13E-F8AD-2541-885D6E2A363B}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B93B412C-BB8F-BE84-F022-A40DDC9D56F0}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1324,7 +1324,7 @@
         <xdr:cNvPr id="2" name="Chart 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{85C6F46E-9BE0-DD2D-92B2-E03FD3C06186}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9A8F0F35-2C10-E1EE-0AED-1B69D4B26031}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1661,7 +1661,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{183A7D64-942A-474A-988C-B4B337309CE5}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FDCE9A2D-4F08-4B4D-B8AE-A5D53F4261D0}">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
@@ -6478,7 +6478,7 @@
         <v>0.1691660000039</v>
       </c>
       <c r="I60" s="73">
-        <v>0.80556346419680003</v>
+        <v>0.16111269283900001</v>
       </c>
       <c r="J60" s="73">
         <v>2.4631687600003001</v>
@@ -6499,7 +6499,7 @@
         <v>5.2864919999899999E-2</v>
       </c>
       <c r="P60" s="73">
-        <v>6.4902901252156999</v>
+        <v>5.8458393538579001</v>
       </c>
       <c r="Q60" s="73">
         <v>5.2960500004000004E-3</v>
@@ -6550,7 +6550,7 @@
         <v>3.6311814424</v>
       </c>
       <c r="AG60" s="73">
-        <v>10.1267676176161</v>
+        <v>9.4823168462582998</v>
       </c>
     </row>
     <row r="61" spans="1:33" x14ac:dyDescent="0.35">
@@ -6957,7 +6957,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{49D3A113-E06F-4C4E-A1ED-A2B7571C770A}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{69B81693-9289-42AA-8C8D-C827098F81FB}">
   <dimension ref="B2:AA4"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
@@ -7135,7 +7135,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{65EF99B4-5433-4C23-8873-268ACC398FA2}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F5585395-ED4C-40FF-BF17-8F5C4DDFC7E3}">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
